--- a/tame_output/ON/bt/strategyON_20231126.xlsx
+++ b/tame_output/ON/bt/strategyON_20231126.xlsx
@@ -610,11 +610,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,12 +623,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>92.2%</t>
+          <t>92.1%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>79.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.9%</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>101.9%</t>
+          <t>101.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>131.6%</t>
+          <t>131.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1792"/>
+  <dimension ref="A1:G1793"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42726,7 +42726,7 @@
         <v>45254</v>
       </c>
       <c r="B1792" t="n">
-        <v>3.157863149879231</v>
+        <v>3.157777201524821</v>
       </c>
       <c r="C1792" t="n">
         <v>3.07155002509494</v>
@@ -42742,6 +42742,29 @@
       </c>
       <c r="G1792" t="n">
         <v>4.376259283321309</v>
+      </c>
+    </row>
+    <row r="1793">
+      <c r="A1793" s="2" t="n">
+        <v>45255</v>
+      </c>
+      <c r="B1793" t="n">
+        <v>3.156246943390047</v>
+      </c>
+      <c r="C1793" t="n">
+        <v>3.071969877157259</v>
+      </c>
+      <c r="D1793" t="n">
+        <v>1.552850161758531</v>
+      </c>
+      <c r="E1793" t="n">
+        <v>3.692753517546925</v>
+      </c>
+      <c r="F1793" t="n">
+        <v>2.175145806749316</v>
+      </c>
+      <c r="G1793" t="n">
+        <v>4.377057361206851</v>
       </c>
     </row>
   </sheetData>
